--- a/media/shoblons/hospital/oth/a_oth_23.xlsx
+++ b/media/shoblons/hospital/oth/a_oth_23.xlsx
@@ -224,7 +224,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -245,11 +245,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -301,7 +296,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -330,10 +325,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -360,9 +351,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:J404"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="74.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="35.85"/>
@@ -503,7 +494,7 @@
       <c r="C14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -521,7 +512,7 @@
       <c r="C16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -530,7 +521,7 @@
       <c r="C17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -539,7 +530,7 @@
       <c r="C18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -548,7 +539,7 @@
       <c r="C19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -557,7 +548,7 @@
       <c r="C20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -566,7 +557,7 @@
       <c r="C21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -584,7 +575,7 @@
       <c r="C23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -593,7 +584,7 @@
       <c r="C24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -602,7 +593,7 @@
       <c r="C25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -611,7 +602,7 @@
       <c r="C26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -620,7 +611,7 @@
       <c r="C27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -629,7 +620,7 @@
       <c r="C28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -647,7 +638,7 @@
       <c r="C30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -656,7 +647,7 @@
       <c r="C31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -665,7 +656,7 @@
       <c r="C32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B33" s="6" t="s">
@@ -674,7 +665,7 @@
       <c r="C33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -683,7 +674,7 @@
       <c r="C34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -692,7 +683,7 @@
       <c r="C35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -701,7 +692,7 @@
       <c r="C36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B37" s="6" t="s">
@@ -719,7 +710,7 @@
       <c r="C38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -728,7 +719,7 @@
       <c r="C39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B40" s="6" t="s">
@@ -737,7 +728,7 @@
       <c r="C40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B41" s="6" t="s">
@@ -746,7 +737,7 @@
       <c r="C41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -755,7 +746,7 @@
       <c r="C42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B43" s="6" t="s">
@@ -764,7 +755,7 @@
       <c r="C43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B44" s="6" t="s">
@@ -782,7 +773,7 @@
       <c r="C45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B46" s="6" t="s">
@@ -791,7 +782,7 @@
       <c r="C46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -800,7 +791,7 @@
       <c r="C47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -809,7 +800,7 @@
       <c r="C48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -818,7 +809,7 @@
       <c r="C49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -827,7 +818,7 @@
       <c r="C50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B51" s="6" t="s">
@@ -836,25 +827,25 @@
       <c r="C51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8"/>
+      <c r="A52" s="7"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8"/>
+      <c r="A53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8"/>
+      <c r="A54" s="7"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="8"/>
+      <c r="A55" s="7"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="8"/>
+      <c r="A56" s="7"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="8"/>
+      <c r="A57" s="7"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="8"/>
+      <c r="A58" s="7"/>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
@@ -863,1050 +854,1050 @@
       <c r="B59" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E59" s="9" t="s">
+      <c r="E59" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="8"/>
+      <c r="A60" s="7"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="8"/>
+      <c r="A61" s="7"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="8"/>
+      <c r="A62" s="7"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="8"/>
+      <c r="A63" s="7"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="8"/>
+      <c r="A64" s="7"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="8"/>
+      <c r="A65" s="7"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="8"/>
+      <c r="A66" s="7"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="8"/>
+      <c r="A67" s="7"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="8"/>
+      <c r="A68" s="7"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="8"/>
+      <c r="A69" s="7"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="8"/>
+      <c r="A70" s="7"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="8"/>
+      <c r="A71" s="7"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="8"/>
+      <c r="A72" s="7"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="8"/>
+      <c r="A73" s="7"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="8"/>
+      <c r="A74" s="7"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="8"/>
+      <c r="A75" s="7"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="8"/>
+      <c r="A76" s="7"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="8"/>
+      <c r="A77" s="7"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="8"/>
+      <c r="A78" s="7"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="8"/>
+      <c r="A79" s="7"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="8"/>
+      <c r="A80" s="7"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="8"/>
+      <c r="A81" s="7"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="8"/>
+      <c r="A82" s="7"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="8"/>
+      <c r="A83" s="7"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="8"/>
+      <c r="A84" s="7"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="8"/>
+      <c r="A85" s="7"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="8"/>
+      <c r="A86" s="7"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="8"/>
+      <c r="A87" s="7"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="8"/>
+      <c r="A88" s="7"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="8"/>
+      <c r="A89" s="7"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="8"/>
+      <c r="A90" s="7"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="8"/>
+      <c r="A91" s="7"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="8"/>
+      <c r="A92" s="7"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="8"/>
+      <c r="A93" s="7"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="8"/>
+      <c r="A94" s="7"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="8"/>
+      <c r="A95" s="7"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="8"/>
+      <c r="A96" s="7"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="8"/>
+      <c r="A97" s="7"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="8"/>
+      <c r="A98" s="7"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="8"/>
+      <c r="A99" s="7"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="8"/>
+      <c r="A100" s="7"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="8"/>
+      <c r="A101" s="7"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="8"/>
+      <c r="A102" s="7"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="8"/>
+      <c r="A103" s="7"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="8"/>
+      <c r="A104" s="7"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="8"/>
+      <c r="A105" s="7"/>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="8"/>
+      <c r="A106" s="7"/>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="8"/>
+      <c r="A107" s="7"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="8"/>
+      <c r="A108" s="7"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="8"/>
+      <c r="A109" s="7"/>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="8"/>
+      <c r="A110" s="7"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="8"/>
+      <c r="A111" s="7"/>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="8"/>
+      <c r="A112" s="7"/>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="8"/>
+      <c r="A113" s="7"/>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="8"/>
+      <c r="A114" s="7"/>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="8"/>
+      <c r="A115" s="7"/>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="8"/>
+      <c r="A116" s="7"/>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="8"/>
+      <c r="A117" s="7"/>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="8"/>
+      <c r="A118" s="7"/>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="8"/>
+      <c r="A119" s="7"/>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="8"/>
+      <c r="A120" s="7"/>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="8"/>
+      <c r="A121" s="7"/>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="8"/>
+      <c r="A122" s="7"/>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="8"/>
+      <c r="A123" s="7"/>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="8"/>
+      <c r="A124" s="7"/>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="8"/>
+      <c r="A125" s="7"/>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="8"/>
+      <c r="A126" s="7"/>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="8"/>
+      <c r="A127" s="7"/>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="8"/>
+      <c r="A128" s="7"/>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="8"/>
+      <c r="A129" s="7"/>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="8"/>
+      <c r="A130" s="7"/>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="8"/>
+      <c r="A131" s="7"/>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="8"/>
+      <c r="A132" s="7"/>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="8"/>
+      <c r="A133" s="7"/>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="8"/>
+      <c r="A134" s="7"/>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="8"/>
+      <c r="A135" s="7"/>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="8"/>
+      <c r="A136" s="7"/>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="8"/>
+      <c r="A137" s="7"/>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="8"/>
+      <c r="A138" s="7"/>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="8"/>
+      <c r="A139" s="7"/>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="8"/>
+      <c r="A140" s="7"/>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="8"/>
+      <c r="A141" s="7"/>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="8"/>
+      <c r="A142" s="7"/>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="8"/>
+      <c r="A143" s="7"/>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="8"/>
+      <c r="A144" s="7"/>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="8"/>
+      <c r="A145" s="7"/>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="8"/>
+      <c r="A146" s="7"/>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="8"/>
+      <c r="A147" s="7"/>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="8"/>
+      <c r="A148" s="7"/>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="8"/>
+      <c r="A149" s="7"/>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="8"/>
+      <c r="A150" s="7"/>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="8"/>
+      <c r="A151" s="7"/>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="8"/>
+      <c r="A152" s="7"/>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="8"/>
+      <c r="A153" s="7"/>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="8"/>
+      <c r="A154" s="7"/>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="8"/>
+      <c r="A155" s="7"/>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="8"/>
+      <c r="A156" s="7"/>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="8"/>
+      <c r="A157" s="7"/>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="8"/>
+      <c r="A158" s="7"/>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="8"/>
+      <c r="A159" s="7"/>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="8"/>
+      <c r="A160" s="7"/>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="8"/>
+      <c r="A161" s="7"/>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="8"/>
+      <c r="A162" s="7"/>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="8"/>
+      <c r="A163" s="7"/>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="8"/>
+      <c r="A164" s="7"/>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="8"/>
+      <c r="A165" s="7"/>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="8"/>
+      <c r="A166" s="7"/>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="8"/>
+      <c r="A167" s="7"/>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="8"/>
+      <c r="A168" s="7"/>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="8"/>
+      <c r="A169" s="7"/>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="8"/>
+      <c r="A170" s="7"/>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="8"/>
+      <c r="A171" s="7"/>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="8"/>
+      <c r="A172" s="7"/>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="8"/>
+      <c r="A173" s="7"/>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="8"/>
+      <c r="A174" s="7"/>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="8"/>
+      <c r="A175" s="7"/>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="8"/>
+      <c r="A176" s="7"/>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="8"/>
+      <c r="A177" s="7"/>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="8"/>
+      <c r="A178" s="7"/>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="8"/>
+      <c r="A179" s="7"/>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="8"/>
+      <c r="A180" s="7"/>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="8"/>
+      <c r="A181" s="7"/>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="8"/>
+      <c r="A182" s="7"/>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="8"/>
+      <c r="A183" s="7"/>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="8"/>
+      <c r="A184" s="7"/>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="8"/>
+      <c r="A185" s="7"/>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="8"/>
+      <c r="A186" s="7"/>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="8"/>
+      <c r="A187" s="7"/>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="8"/>
+      <c r="A188" s="7"/>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="8"/>
+      <c r="A189" s="7"/>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="8"/>
+      <c r="A190" s="7"/>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="8"/>
+      <c r="A191" s="7"/>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="8"/>
+      <c r="A192" s="7"/>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="8"/>
+      <c r="A193" s="7"/>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="8"/>
+      <c r="A194" s="7"/>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="8"/>
+      <c r="A195" s="7"/>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="8"/>
+      <c r="A196" s="7"/>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="8"/>
+      <c r="A197" s="7"/>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="8"/>
+      <c r="A198" s="7"/>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="8"/>
+      <c r="A199" s="7"/>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="8"/>
+      <c r="A200" s="7"/>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="8"/>
+      <c r="A201" s="7"/>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="8"/>
+      <c r="A202" s="7"/>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="8"/>
+      <c r="A203" s="7"/>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="8"/>
+      <c r="A204" s="7"/>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="8"/>
+      <c r="A205" s="7"/>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="8"/>
+      <c r="A206" s="7"/>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="8"/>
+      <c r="A207" s="7"/>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="8"/>
+      <c r="A208" s="7"/>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="8"/>
+      <c r="A209" s="7"/>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="8"/>
+      <c r="A210" s="7"/>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="8"/>
+      <c r="A211" s="7"/>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="8"/>
+      <c r="A212" s="7"/>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="8"/>
+      <c r="A213" s="7"/>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="8"/>
+      <c r="A214" s="7"/>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="8"/>
+      <c r="A215" s="7"/>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="8"/>
+      <c r="A216" s="7"/>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="8"/>
+      <c r="A217" s="7"/>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="8"/>
+      <c r="A218" s="7"/>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="8"/>
+      <c r="A219" s="7"/>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="8"/>
+      <c r="A220" s="7"/>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="8"/>
+      <c r="A221" s="7"/>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="8"/>
+      <c r="A222" s="7"/>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="8"/>
+      <c r="A223" s="7"/>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="8"/>
+      <c r="A224" s="7"/>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="8"/>
+      <c r="A225" s="7"/>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="8"/>
+      <c r="A226" s="7"/>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="8"/>
+      <c r="A227" s="7"/>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="8"/>
+      <c r="A228" s="7"/>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="8"/>
+      <c r="A229" s="7"/>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="8"/>
+      <c r="A230" s="7"/>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="8"/>
+      <c r="A231" s="7"/>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="8"/>
+      <c r="A232" s="7"/>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="8"/>
+      <c r="A233" s="7"/>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="8"/>
+      <c r="A234" s="7"/>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="8"/>
+      <c r="A235" s="7"/>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="8"/>
+      <c r="A236" s="7"/>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="8"/>
+      <c r="A237" s="7"/>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="8"/>
+      <c r="A238" s="7"/>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="8"/>
+      <c r="A239" s="7"/>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="8"/>
+      <c r="A240" s="7"/>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="8"/>
+      <c r="A241" s="7"/>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="8"/>
+      <c r="A242" s="7"/>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="8"/>
+      <c r="A243" s="7"/>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="8"/>
+      <c r="A244" s="7"/>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="8"/>
+      <c r="A245" s="7"/>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="8"/>
+      <c r="A246" s="7"/>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="8"/>
+      <c r="A247" s="7"/>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="8"/>
+      <c r="A248" s="7"/>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="8"/>
+      <c r="A249" s="7"/>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="8"/>
+      <c r="A250" s="7"/>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="8"/>
+      <c r="A251" s="7"/>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="8"/>
+      <c r="A252" s="7"/>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="8"/>
+      <c r="A253" s="7"/>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="8"/>
+      <c r="A254" s="7"/>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="8"/>
+      <c r="A255" s="7"/>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="8"/>
+      <c r="A256" s="7"/>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="8"/>
+      <c r="A257" s="7"/>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="8"/>
+      <c r="A258" s="7"/>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="8"/>
+      <c r="A259" s="7"/>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="8"/>
+      <c r="A260" s="7"/>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="8"/>
+      <c r="A261" s="7"/>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="8"/>
+      <c r="A262" s="7"/>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="8"/>
+      <c r="A263" s="7"/>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="8"/>
+      <c r="A264" s="7"/>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="8"/>
+      <c r="A265" s="7"/>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="8"/>
+      <c r="A266" s="7"/>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="8"/>
+      <c r="A267" s="7"/>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="8"/>
+      <c r="A268" s="7"/>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="8"/>
+      <c r="A269" s="7"/>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="8"/>
+      <c r="A270" s="7"/>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="8"/>
+      <c r="A271" s="7"/>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="8"/>
+      <c r="A272" s="7"/>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="8"/>
+      <c r="A273" s="7"/>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="8"/>
+      <c r="A274" s="7"/>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="8"/>
+      <c r="A275" s="7"/>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="8"/>
+      <c r="A276" s="7"/>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="8"/>
+      <c r="A277" s="7"/>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="8"/>
+      <c r="A278" s="7"/>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="8"/>
+      <c r="A279" s="7"/>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="8"/>
+      <c r="A280" s="7"/>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="8"/>
+      <c r="A281" s="7"/>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="8"/>
+      <c r="A282" s="7"/>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="8"/>
+      <c r="A283" s="7"/>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="8"/>
+      <c r="A284" s="7"/>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="8"/>
+      <c r="A285" s="7"/>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="8"/>
+      <c r="A286" s="7"/>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="8"/>
+      <c r="A287" s="7"/>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="8"/>
+      <c r="A288" s="7"/>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="8"/>
+      <c r="A289" s="7"/>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="8"/>
+      <c r="A290" s="7"/>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="8"/>
+      <c r="A291" s="7"/>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="8"/>
+      <c r="A292" s="7"/>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="8"/>
+      <c r="A293" s="7"/>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="8"/>
+      <c r="A294" s="7"/>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="8"/>
+      <c r="A295" s="7"/>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="8"/>
+      <c r="A296" s="7"/>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="8"/>
+      <c r="A297" s="7"/>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="8"/>
+      <c r="A298" s="7"/>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="8"/>
+      <c r="A299" s="7"/>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="8"/>
+      <c r="A300" s="7"/>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="8"/>
+      <c r="A301" s="7"/>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="8"/>
+      <c r="A302" s="7"/>
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="8"/>
+      <c r="A303" s="7"/>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="8"/>
+      <c r="A304" s="7"/>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="8"/>
+      <c r="A305" s="7"/>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A306" s="8"/>
+      <c r="A306" s="7"/>
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A307" s="8"/>
+      <c r="A307" s="7"/>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A308" s="8"/>
+      <c r="A308" s="7"/>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="8"/>
+      <c r="A309" s="7"/>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="8"/>
+      <c r="A310" s="7"/>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A311" s="8"/>
+      <c r="A311" s="7"/>
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A312" s="8"/>
+      <c r="A312" s="7"/>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="8"/>
+      <c r="A313" s="7"/>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="8"/>
+      <c r="A314" s="7"/>
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A315" s="8"/>
+      <c r="A315" s="7"/>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="8"/>
+      <c r="A316" s="7"/>
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="8"/>
+      <c r="A317" s="7"/>
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A318" s="8"/>
+      <c r="A318" s="7"/>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="8"/>
+      <c r="A319" s="7"/>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A320" s="8"/>
+      <c r="A320" s="7"/>
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A321" s="8"/>
+      <c r="A321" s="7"/>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A322" s="8"/>
+      <c r="A322" s="7"/>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="8"/>
+      <c r="A323" s="7"/>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="8"/>
+      <c r="A324" s="7"/>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A325" s="8"/>
+      <c r="A325" s="7"/>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="8"/>
+      <c r="A326" s="7"/>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A327" s="8"/>
+      <c r="A327" s="7"/>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="8"/>
+      <c r="A328" s="7"/>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A329" s="8"/>
+      <c r="A329" s="7"/>
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="8"/>
+      <c r="A330" s="7"/>
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A331" s="8"/>
+      <c r="A331" s="7"/>
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A332" s="8"/>
+      <c r="A332" s="7"/>
     </row>
     <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="8"/>
+      <c r="A333" s="7"/>
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="8"/>
+      <c r="A334" s="7"/>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A335" s="8"/>
+      <c r="A335" s="7"/>
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="8"/>
+      <c r="A336" s="7"/>
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A337" s="8"/>
+      <c r="A337" s="7"/>
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="8"/>
+      <c r="A338" s="7"/>
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="8"/>
+      <c r="A339" s="7"/>
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="8"/>
+      <c r="A340" s="7"/>
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="8"/>
+      <c r="A341" s="7"/>
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="8"/>
+      <c r="A342" s="7"/>
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="8"/>
+      <c r="A343" s="7"/>
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A344" s="8"/>
+      <c r="A344" s="7"/>
     </row>
     <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="8"/>
+      <c r="A345" s="7"/>
     </row>
     <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A346" s="8"/>
+      <c r="A346" s="7"/>
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A347" s="8"/>
+      <c r="A347" s="7"/>
     </row>
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A348" s="8"/>
+      <c r="A348" s="7"/>
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A349" s="8"/>
+      <c r="A349" s="7"/>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A350" s="8"/>
+      <c r="A350" s="7"/>
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A351" s="8"/>
+      <c r="A351" s="7"/>
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A352" s="8"/>
+      <c r="A352" s="7"/>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A353" s="8"/>
+      <c r="A353" s="7"/>
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A354" s="8"/>
+      <c r="A354" s="7"/>
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A355" s="8"/>
+      <c r="A355" s="7"/>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A356" s="8"/>
+      <c r="A356" s="7"/>
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A357" s="8"/>
+      <c r="A357" s="7"/>
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A358" s="8"/>
+      <c r="A358" s="7"/>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A359" s="8"/>
+      <c r="A359" s="7"/>
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A360" s="8"/>
+      <c r="A360" s="7"/>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A361" s="8"/>
+      <c r="A361" s="7"/>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A362" s="8"/>
+      <c r="A362" s="7"/>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A363" s="8"/>
+      <c r="A363" s="7"/>
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A364" s="8"/>
+      <c r="A364" s="7"/>
     </row>
     <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A365" s="8"/>
+      <c r="A365" s="7"/>
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A366" s="8"/>
+      <c r="A366" s="7"/>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A367" s="8"/>
+      <c r="A367" s="7"/>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="8"/>
+      <c r="A368" s="7"/>
     </row>
     <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="8"/>
+      <c r="A369" s="7"/>
     </row>
     <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A370" s="8"/>
+      <c r="A370" s="7"/>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A371" s="8"/>
+      <c r="A371" s="7"/>
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A372" s="8"/>
+      <c r="A372" s="7"/>
     </row>
     <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A373" s="8"/>
+      <c r="A373" s="7"/>
     </row>
     <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A374" s="8"/>
+      <c r="A374" s="7"/>
     </row>
     <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A375" s="8"/>
+      <c r="A375" s="7"/>
     </row>
     <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A376" s="8"/>
+      <c r="A376" s="7"/>
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A377" s="8"/>
+      <c r="A377" s="7"/>
     </row>
     <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A378" s="8"/>
+      <c r="A378" s="7"/>
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A379" s="8"/>
+      <c r="A379" s="7"/>
     </row>
     <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A380" s="8"/>
+      <c r="A380" s="7"/>
     </row>
     <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A381" s="8"/>
+      <c r="A381" s="7"/>
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A382" s="8"/>
+      <c r="A382" s="7"/>
     </row>
     <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A383" s="8"/>
+      <c r="A383" s="7"/>
     </row>
     <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A384" s="8"/>
+      <c r="A384" s="7"/>
     </row>
     <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A385" s="8"/>
+      <c r="A385" s="7"/>
     </row>
     <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A386" s="8"/>
+      <c r="A386" s="7"/>
     </row>
     <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A387" s="8"/>
+      <c r="A387" s="7"/>
     </row>
     <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A388" s="8"/>
+      <c r="A388" s="7"/>
     </row>
     <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A389" s="8"/>
+      <c r="A389" s="7"/>
     </row>
     <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A390" s="8"/>
+      <c r="A390" s="7"/>
     </row>
     <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A391" s="8"/>
+      <c r="A391" s="7"/>
     </row>
     <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A392" s="8"/>
+      <c r="A392" s="7"/>
     </row>
     <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A393" s="8"/>
+      <c r="A393" s="7"/>
     </row>
     <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A394" s="8"/>
+      <c r="A394" s="7"/>
     </row>
     <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A395" s="8"/>
+      <c r="A395" s="7"/>
     </row>
     <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A396" s="8"/>
+      <c r="A396" s="7"/>
     </row>
     <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A397" s="8"/>
+      <c r="A397" s="7"/>
     </row>
     <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A398" s="8"/>
+      <c r="A398" s="7"/>
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A399" s="8"/>
+      <c r="A399" s="7"/>
     </row>
     <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A400" s="8"/>
+      <c r="A400" s="7"/>
     </row>
     <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A401" s="8"/>
+      <c r="A401" s="7"/>
     </row>
     <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A402" s="8"/>
+      <c r="A402" s="7"/>
     </row>
     <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A403" s="8"/>
+      <c r="A403" s="7"/>
     </row>
     <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A404" s="8"/>
+      <c r="A404" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1916,10 +1907,10 @@
     <mergeCell ref="A5:E5"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.157638888888889" right="0.157638888888889" top="0.7875" bottom="1.05277777777778" header="0.511811023622047" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
+    <oddHeader/>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
